--- a/experiments/results/resnet18/CIFAR-10/ReAct/adaptive/avg/results.xlsx
+++ b/experiments/results/resnet18/CIFAR-10/ReAct/adaptive/avg/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -862,6 +862,153 @@
       <c r="O10" s="5" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=None,react_th=0.5,scale_th=0.05,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>17.47</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>96.92</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>91.33</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>96.98999999999999</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>95.31</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>98.23999999999999</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>16.41</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>97.11</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>21.69</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>95.98</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.3,scale_th=0.05,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>27.15</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>94.88</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>89.06999999999999</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>34.26</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>92.58</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>95.65000000000001</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>95.41</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>93.83</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.2,scale_th=0.05,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>15.74</v>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>97.29000000000001</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>42.15</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>97.31</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>23.87</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>95.92</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>98.84</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>96.42</v>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=None,react_th=0.4,scale_th=0.05,type=avg</t>
         </is>
       </c>
     </row>
